--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,168 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>185720056</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>152641980</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41139543</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26449868</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21951647</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9189819</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,6 +777,168 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>185720056</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>152641980</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>41139543</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26449868</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21951647</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9189819</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,168 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>185720056</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>152641980</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41139543</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>26449868</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="D24" t="n">
+        <v>21951647</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9189819</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,168 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>185720056</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>152641980</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41139543</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26449868</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="D30" t="n">
+        <v>21951647</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9189819</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,6 +1263,168 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>185720056</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>152641980</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>41139543</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>26449868</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="D36" t="n">
+        <v>21951647</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9189819</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,168 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="D38" t="n">
+        <v>116609036</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="D39" t="n">
+        <v>107298258</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>41368475</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>29650908</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>29502376</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12750622</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,144 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>116609036</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>107298258</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>41368475</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>29650908</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>29502376</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>12750622</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,6 +1725,141 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D50" t="n">
+        <v>124665096</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="D51" t="n">
+        <v>63644141</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>462.2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>26592706</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>20209776</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>13670333</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1860,6 +1860,144 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>192341775</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>89701722</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>33738701</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>30810678</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>18431512</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>12111898</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,6 +1998,168 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="D61" t="n">
+        <v>176292806</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="D62" t="n">
+        <v>109868643</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>34280540</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="D64" t="n">
+        <v>25163892</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>18927606</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7692378</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2160,6 +2160,144 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>188026592</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>117068449</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>45119186</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>39654395</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>21982614</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>16983186</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,6 +2298,144 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>196298555</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>100972558</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>39787270</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>23999519</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>18583483</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>18267433</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2436,6 +2436,168 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D79" t="n">
+        <v>196195555</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" t="n">
+        <v>100960958</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="D81" t="n">
+        <v>39784370</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="D82" t="n">
+        <v>23998219</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="D83" t="n">
+        <v>18580283</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D84" t="n">
+        <v>18267233</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2598,6 +2598,168 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D85" t="n">
+        <v>196195555</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>30</v>
+      </c>
+      <c r="D86" t="n">
+        <v>100960958</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="D87" t="n">
+        <v>39784370</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>23998219</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="D89" t="n">
+        <v>18580283</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D90" t="n">
+        <v>18267233</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2760,6 +2760,168 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D91" t="n">
+        <v>196195555</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>30</v>
+      </c>
+      <c r="D92" t="n">
+        <v>100960958</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="D93" t="n">
+        <v>39784370</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="D94" t="n">
+        <v>23998219</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="D95" t="n">
+        <v>18580283</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D96" t="n">
+        <v>18267233</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +2922,168 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="D97" t="n">
+        <v>253253893</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="D98" t="n">
+        <v>148283733</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>67357066</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>439</v>
+      </c>
+      <c r="D100" t="n">
+        <v>32795639</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="D101" t="n">
+        <v>32533024</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D102" t="n">
+        <v>19646590</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3084,6 +3084,168 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>283417486</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="D104" t="n">
+        <v>246730455</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>34078568</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>32965656</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>434.4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>24863984</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>146.6</v>
+      </c>
+      <c r="D108" t="n">
+        <v>14520391</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3246,6 +3246,168 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="D109" t="n">
+        <v>319921929</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="D110" t="n">
+        <v>238003859</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>94713412</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>425</v>
+      </c>
+      <c r="D112" t="n">
+        <v>42196103</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="D113" t="n">
+        <v>30571211</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="D114" t="n">
+        <v>17372582</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3408,6 +3408,168 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1230798186</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D116" t="n">
+        <v>248812612</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="D117" t="n">
+        <v>81724196</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D118" t="n">
+        <v>50503512</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>48005475</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>13019970</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3570,6 +3570,168 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1230798186</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D122" t="n">
+        <v>248812612</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="D123" t="n">
+        <v>81724196</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D124" t="n">
+        <v>50503512</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>48005475</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>13019970</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,6 +3732,168 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1230798186</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D128" t="n">
+        <v>248812612</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="D129" t="n">
+        <v>81724196</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D130" t="n">
+        <v>50503512</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>48005475</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>13019970</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,6 +3894,172 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>350866907</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="D134" t="n">
+        <v>164616523</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="D135" t="n">
+        <v>72625452</v>
+      </c>
+      <c r="E135" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>436</v>
+      </c>
+      <c r="D136" t="n">
+        <v>35164391</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D137" t="n">
+        <v>24241377</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>11125038</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4060,6 +4060,184 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="D139" t="n">
+        <v>202874745</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="D140" t="n">
+        <v>178513477</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="D141" t="n">
+        <v>136662320</v>
+      </c>
+      <c r="E141" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>481.6</v>
+      </c>
+      <c r="D142" t="n">
+        <v>101874275</v>
+      </c>
+      <c r="E142" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="D143" t="n">
+        <v>44730548</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>17445189</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4238,6 +4238,168 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="D145" t="n">
+        <v>173013055</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="D146" t="n">
+        <v>142370227</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D147" t="n">
+        <v>83942077</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="D148" t="n">
+        <v>49104320</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="D149" t="n">
+        <v>28148039</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="D150" t="n">
+        <v>13176862</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4400,6 +4400,168 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D151" t="n">
+        <v>172993390</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="D152" t="n">
+        <v>88262656</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="D153" t="n">
+        <v>43047835</v>
+      </c>
+      <c r="E153" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>459</v>
+      </c>
+      <c r="D154" t="n">
+        <v>29053909</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D155" t="n">
+        <v>24773902</v>
+      </c>
+      <c r="E155" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="D156" t="n">
+        <v>11968429</v>
+      </c>
+      <c r="E156" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4562,6 +4562,144 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>219025562</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>154077195</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>57510319</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>31649780</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>29293119</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>26158535</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,6 +4700,168 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="D163" t="n">
+        <v>219022562</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D164" t="n">
+        <v>154054795</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="D165" t="n">
+        <v>57489919</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>453.2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>31649780</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="D167" t="n">
+        <v>29293119</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D168" t="n">
+        <v>26150935</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4862,6 +4862,168 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="D169" t="n">
+        <v>219022562</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D170" t="n">
+        <v>154054795</v>
+      </c>
+      <c r="E170" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="D171" t="n">
+        <v>57489919</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>453.2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>31649780</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="D173" t="n">
+        <v>29293119</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D174" t="n">
+        <v>26150935</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5024,6 +5024,168 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="D175" t="n">
+        <v>249094895</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="D176" t="n">
+        <v>152036878</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="D177" t="n">
+        <v>63060620</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="D178" t="n">
+        <v>29019096</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D179" t="n">
+        <v>25945048</v>
+      </c>
+      <c r="E179" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>15193347</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5186,6 +5186,144 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="n">
+        <v>246117414</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="n">
+        <v>103973917</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>37388999</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="n">
+        <v>34274279</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="n">
+        <v>14799866</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="n">
+        <v>11631298</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5324,6 +5324,168 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D187" t="n">
+        <v>239320135</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="D188" t="n">
+        <v>226252092</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>79</v>
+      </c>
+      <c r="D189" t="n">
+        <v>56328337</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>465.6</v>
+      </c>
+      <c r="D190" t="n">
+        <v>35788237</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="D191" t="n">
+        <v>35400697</v>
+      </c>
+      <c r="E191" t="n">
+        <v>-4.79</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="D192" t="n">
+        <v>33622524</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,6 +5486,168 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="D193" t="n">
+        <v>205357363</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="D194" t="n">
+        <v>124356371</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="D195" t="n">
+        <v>34922354</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>457.2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>28580619</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="D197" t="n">
+        <v>20844023</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="D198" t="n">
+        <v>17746424</v>
+      </c>
+      <c r="E198" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5648,6 +5648,144 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="n">
+        <v>248112067</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="n">
+        <v>131885183</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="n">
+        <v>47409244</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="n">
+        <v>22348046</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="n">
+        <v>16499792</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="n">
+        <v>14737451</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,6 +5786,176 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="D205" t="n">
+        <v>247996067</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D206" t="n">
+        <v>131880583</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D207" t="n">
+        <v>47407244</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>463.6</v>
+      </c>
+      <c r="D208" t="n">
+        <v>22334646</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="D209" t="n">
+        <v>16484892</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="D210" t="n">
+        <v>14715851</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5956,6 +5956,176 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="D211" t="n">
+        <v>247996067</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D212" t="n">
+        <v>131880583</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D213" t="n">
+        <v>47407244</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>463.6</v>
+      </c>
+      <c r="D214" t="n">
+        <v>22334646</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="D215" t="n">
+        <v>16484892</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>14715851</v>
+      </c>
+      <c r="E216" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6126,6 +6126,168 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="D217" t="n">
+        <v>213683528</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="D218" t="n">
+        <v>94791143</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="D219" t="n">
+        <v>24420487</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>459.6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>19749038</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D221" t="n">
+        <v>19539835</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="D222" t="n">
+        <v>19098018</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6288,6 +6288,168 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D223" t="n">
+        <v>207688432</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D224" t="n">
+        <v>113820844</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="D225" t="n">
+        <v>40106007</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>447.4</v>
+      </c>
+      <c r="D226" t="n">
+        <v>24325342</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="D227" t="n">
+        <v>17291496</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>146</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10893838</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6450,6 +6450,168 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D229" t="n">
+        <v>207688432</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D230" t="n">
+        <v>113820844</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="D231" t="n">
+        <v>40106007</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>447.4</v>
+      </c>
+      <c r="D232" t="n">
+        <v>24325342</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="D233" t="n">
+        <v>17291496</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>146</v>
+      </c>
+      <c r="D234" t="n">
+        <v>10893838</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6612,6 +6612,168 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="D235" t="n">
+        <v>199417941</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="D236" t="n">
+        <v>109311295</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="D237" t="n">
+        <v>26625914</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D238" t="n">
+        <v>22509016</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>148</v>
+      </c>
+      <c r="D239" t="n">
+        <v>20033826</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>445.4</v>
+      </c>
+      <c r="D240" t="n">
+        <v>16962934</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6774,6 +6774,168 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D241" t="n">
+        <v>336421078</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="D242" t="n">
+        <v>199676198</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D243" t="n">
+        <v>68422090</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="D244" t="n">
+        <v>30921772</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="D245" t="n">
+        <v>30133517</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>149</v>
+      </c>
+      <c r="D246" t="n">
+        <v>28019812</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6936,6 +6936,168 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D247" t="n">
+        <v>335563078</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="D248" t="n">
+        <v>199675798</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D249" t="n">
+        <v>68421090</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="D250" t="n">
+        <v>30913072</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="D251" t="n">
+        <v>30119117</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>149</v>
+      </c>
+      <c r="D252" t="n">
+        <v>28019812</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7098,6 +7098,168 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D253" t="n">
+        <v>335563078</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="D254" t="n">
+        <v>199675798</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D255" t="n">
+        <v>68421090</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="D256" t="n">
+        <v>30913072</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="D257" t="n">
+        <v>30119117</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>149</v>
+      </c>
+      <c r="D258" t="n">
+        <v>28019812</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7260,6 +7260,168 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="D259" t="n">
+        <v>335563078</v>
+      </c>
+      <c r="E259" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="D260" t="n">
+        <v>199675798</v>
+      </c>
+      <c r="E260" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D261" t="n">
+        <v>68421090</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="D262" t="n">
+        <v>30913072</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="D263" t="n">
+        <v>30119117</v>
+      </c>
+      <c r="E263" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>149</v>
+      </c>
+      <c r="D264" t="n">
+        <v>28019812</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G264"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7422,6 +7422,168 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="D265" t="n">
+        <v>281837072</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="D266" t="n">
+        <v>241867064</v>
+      </c>
+      <c r="E266" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>72</v>
+      </c>
+      <c r="D267" t="n">
+        <v>57155017</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="D268" t="n">
+        <v>40013285</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>433</v>
+      </c>
+      <c r="D269" t="n">
+        <v>31563511</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D270" t="n">
+        <v>11433704</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7584,6 +7584,168 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D271" t="n">
+        <v>244562008</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="D272" t="n">
+        <v>240187381</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D273" t="n">
+        <v>43435989</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="D274" t="n">
+        <v>38196900</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="D275" t="n">
+        <v>33271403</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="D276" t="n">
+        <v>14753307</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7746,6 +7746,172 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="D277" t="n">
+        <v>253211961</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D278" t="n">
+        <v>219958418</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="D279" t="n">
+        <v>53084562</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>428.8</v>
+      </c>
+      <c r="D280" t="n">
+        <v>39960188</v>
+      </c>
+      <c r="E280" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="D281" t="n">
+        <v>27134039</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="D282" t="n">
+        <v>10676559</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7912,6 +7912,168 @@
         </is>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D283" t="n">
+        <v>296655004</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D284" t="n">
+        <v>178979826</v>
+      </c>
+      <c r="E284" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="D285" t="n">
+        <v>63246885</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="D286" t="n">
+        <v>29475228</v>
+      </c>
+      <c r="E286" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="D287" t="n">
+        <v>28179889</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="D288" t="n">
+        <v>8640496</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8074,6 +8074,168 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="D289" t="n">
+        <v>302272122</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D290" t="n">
+        <v>191629568</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="D291" t="n">
+        <v>84458170</v>
+      </c>
+      <c r="E291" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="D292" t="n">
+        <v>32626256</v>
+      </c>
+      <c r="E292" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D293" t="n">
+        <v>31873009</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="D294" t="n">
+        <v>17958541</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G294"/>
+  <dimension ref="A1:G300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8236,6 +8236,168 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="D295" t="n">
+        <v>301316122</v>
+      </c>
+      <c r="E295" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D296" t="n">
+        <v>191622768</v>
+      </c>
+      <c r="E296" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="D297" t="n">
+        <v>84453570</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="D298" t="n">
+        <v>32623656</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D299" t="n">
+        <v>31872909</v>
+      </c>
+      <c r="E299" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="D300" t="n">
+        <v>17958141</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8398,6 +8398,168 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="D301" t="n">
+        <v>301316122</v>
+      </c>
+      <c r="E301" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D302" t="n">
+        <v>191622768</v>
+      </c>
+      <c r="E302" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="D303" t="n">
+        <v>84453570</v>
+      </c>
+      <c r="E303" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="D304" t="n">
+        <v>32623656</v>
+      </c>
+      <c r="E304" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="D305" t="n">
+        <v>31872909</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="D306" t="n">
+        <v>17958141</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8560,6 +8560,172 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="D307" t="n">
+        <v>206098162</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="D308" t="n">
+        <v>203630574</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="D309" t="n">
+        <v>79469292</v>
+      </c>
+      <c r="E309" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>420.2</v>
+      </c>
+      <c r="D310" t="n">
+        <v>33068270</v>
+      </c>
+      <c r="E310" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D311" t="n">
+        <v>24806382</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="D312" t="n">
+        <v>14017945</v>
+      </c>
+      <c r="E312" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8726,6 +8726,168 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D313" t="n">
+        <v>446083435</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D314" t="n">
+        <v>173878474</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>65133829</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="D316" t="n">
+        <v>38994509</v>
+      </c>
+      <c r="E316" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="D317" t="n">
+        <v>28317939</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D318" t="n">
+        <v>13125169</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8888,6 +8888,168 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D319" t="n">
+        <v>446077435</v>
+      </c>
+      <c r="E319" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D320" t="n">
+        <v>173878074</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="D321" t="n">
+        <v>65133829</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="D322" t="n">
+        <v>38994409</v>
+      </c>
+      <c r="E322" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="D323" t="n">
+        <v>28317739</v>
+      </c>
+      <c r="E323" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D324" t="n">
+        <v>13123569</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9050,6 +9050,180 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="D325" t="n">
+        <v>347782413</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D326" t="n">
+        <v>222813369</v>
+      </c>
+      <c r="E326" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="D327" t="n">
+        <v>68123030</v>
+      </c>
+      <c r="E327" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D328" t="n">
+        <v>54576171</v>
+      </c>
+      <c r="E328" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>430.2</v>
+      </c>
+      <c r="D329" t="n">
+        <v>40905200</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="D330" t="n">
+        <v>18648715</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G330"/>
+  <dimension ref="A1:G336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9224,6 +9224,172 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D331" t="n">
+        <v>268236962</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="D332" t="n">
+        <v>226825441</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="D333" t="n">
+        <v>54233110</v>
+      </c>
+      <c r="E333" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D334" t="n">
+        <v>33746748</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>152</v>
+      </c>
+      <c r="D335" t="n">
+        <v>29830805</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>431.2</v>
+      </c>
+      <c r="D336" t="n">
+        <v>24957596</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G336"/>
+  <dimension ref="A1:G342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9390,6 +9390,172 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D337" t="n">
+        <v>268232162</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="D338" t="n">
+        <v>226824441</v>
+      </c>
+      <c r="E338" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="D339" t="n">
+        <v>54232910</v>
+      </c>
+      <c r="E339" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D340" t="n">
+        <v>33741448</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>152</v>
+      </c>
+      <c r="D341" t="n">
+        <v>29828005</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>431.2</v>
+      </c>
+      <c r="D342" t="n">
+        <v>24957296</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9556,6 +9556,172 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D343" t="n">
+        <v>268232162</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="D344" t="n">
+        <v>226824441</v>
+      </c>
+      <c r="E344" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="D345" t="n">
+        <v>54232910</v>
+      </c>
+      <c r="E345" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D346" t="n">
+        <v>33741448</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>152</v>
+      </c>
+      <c r="D347" t="n">
+        <v>29828005</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>431.2</v>
+      </c>
+      <c r="D348" t="n">
+        <v>24957296</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9722,6 +9722,176 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="D349" t="n">
+        <v>204470175</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="D350" t="n">
+        <v>160206188</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="D351" t="n">
+        <v>50532484</v>
+      </c>
+      <c r="E351" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>452</v>
+      </c>
+      <c r="D352" t="n">
+        <v>41502283</v>
+      </c>
+      <c r="E352" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="D353" t="n">
+        <v>36021501</v>
+      </c>
+      <c r="E353" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>152</v>
+      </c>
+      <c r="D354" t="n">
+        <v>11330076</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G354"/>
+  <dimension ref="A1:G360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9892,6 +9892,172 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D355" t="n">
+        <v>202757949</v>
+      </c>
+      <c r="E355" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="D356" t="n">
+        <v>194336167</v>
+      </c>
+      <c r="E356" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="D357" t="n">
+        <v>117136479</v>
+      </c>
+      <c r="E357" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>461.2</v>
+      </c>
+      <c r="D358" t="n">
+        <v>55418634</v>
+      </c>
+      <c r="E358" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>83.45</v>
+      </c>
+      <c r="D359" t="n">
+        <v>26025082</v>
+      </c>
+      <c r="E359" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="D360" t="n">
+        <v>13821429</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10058,6 +10058,184 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D361" t="n">
+        <v>409721793</v>
+      </c>
+      <c r="E361" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D362" t="n">
+        <v>291435740</v>
+      </c>
+      <c r="E362" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D363" t="n">
+        <v>72751380</v>
+      </c>
+      <c r="E363" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="D364" t="n">
+        <v>56278727</v>
+      </c>
+      <c r="E364" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="D365" t="n">
+        <v>26821234</v>
+      </c>
+      <c r="E365" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="D366" t="n">
+        <v>10813938</v>
+      </c>
+      <c r="E366" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10236,6 +10236,168 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>25</v>
+      </c>
+      <c r="D367" t="n">
+        <v>348624328</v>
+      </c>
+      <c r="E367" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="D368" t="n">
+        <v>212661134</v>
+      </c>
+      <c r="E368" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D369" t="n">
+        <v>55806031</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>469.6</v>
+      </c>
+      <c r="D370" t="n">
+        <v>42402252</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="D371" t="n">
+        <v>38997658</v>
+      </c>
+      <c r="E371" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="D372" t="n">
+        <v>8992816</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G372"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10398,6 +10398,172 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="D373" t="n">
+        <v>254499994</v>
+      </c>
+      <c r="E373" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D374" t="n">
+        <v>157134844</v>
+      </c>
+      <c r="E374" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="D375" t="n">
+        <v>40440798</v>
+      </c>
+      <c r="E375" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D376" t="n">
+        <v>38060521</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D377" t="n">
+        <v>23566417</v>
+      </c>
+      <c r="E377" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D378" t="n">
+        <v>11228812</v>
+      </c>
+      <c r="E378" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10564,6 +10564,172 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="D379" t="n">
+        <v>254498794</v>
+      </c>
+      <c r="E379" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D380" t="n">
+        <v>157131844</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="D381" t="n">
+        <v>40440298</v>
+      </c>
+      <c r="E381" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D382" t="n">
+        <v>38059821</v>
+      </c>
+      <c r="E382" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D383" t="n">
+        <v>23565217</v>
+      </c>
+      <c r="E383" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D384" t="n">
+        <v>11223212</v>
+      </c>
+      <c r="E384" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:G390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10730,6 +10730,172 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="D385" t="n">
+        <v>254498794</v>
+      </c>
+      <c r="E385" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D386" t="n">
+        <v>157131844</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="D387" t="n">
+        <v>40440298</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="D388" t="n">
+        <v>38059821</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D389" t="n">
+        <v>23565217</v>
+      </c>
+      <c r="E389" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="D390" t="n">
+        <v>11223212</v>
+      </c>
+      <c r="E390" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:G396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10896,6 +10896,168 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="D391" t="n">
+        <v>206565061</v>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D392" t="n">
+        <v>166773706</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="D393" t="n">
+        <v>40168127</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>457.6</v>
+      </c>
+      <c r="D394" t="n">
+        <v>24291942</v>
+      </c>
+      <c r="E394" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="D395" t="n">
+        <v>15518597</v>
+      </c>
+      <c r="E395" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="D396" t="n">
+        <v>7634322</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G396"/>
+  <dimension ref="A1:G402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11058,6 +11058,168 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="D397" t="n">
+        <v>235765661</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="D398" t="n">
+        <v>166094532</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D399" t="n">
+        <v>50007153</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>456.2</v>
+      </c>
+      <c r="D400" t="n">
+        <v>25540840</v>
+      </c>
+      <c r="E400" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D401" t="n">
+        <v>23042274</v>
+      </c>
+      <c r="E401" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="D402" t="n">
+        <v>10673356</v>
+      </c>
+      <c r="E402" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G402"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11220,6 +11220,176 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="D403" t="n">
+        <v>197107218</v>
+      </c>
+      <c r="E403" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="D404" t="n">
+        <v>151795385</v>
+      </c>
+      <c r="E404" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="D405" t="n">
+        <v>88087018</v>
+      </c>
+      <c r="E405" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>474</v>
+      </c>
+      <c r="D406" t="n">
+        <v>33782856</v>
+      </c>
+      <c r="E406" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="D407" t="n">
+        <v>18754137</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="D408" t="n">
+        <v>15261193</v>
+      </c>
+      <c r="E408" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11390,6 +11390,180 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D409" t="n">
+        <v>319311911</v>
+      </c>
+      <c r="E409" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="D410" t="n">
+        <v>216414488</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="D411" t="n">
+        <v>100388958</v>
+      </c>
+      <c r="E411" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>484</v>
+      </c>
+      <c r="D412" t="n">
+        <v>42851575</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="D413" t="n">
+        <v>34557521</v>
+      </c>
+      <c r="E413" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D414" t="n">
+        <v>13901518</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G414"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11564,6 +11564,168 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="D415" t="n">
+        <v>279985322</v>
+      </c>
+      <c r="E415" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D416" t="n">
+        <v>246024201</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="D417" t="n">
+        <v>79212929</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="D418" t="n">
+        <v>36238357</v>
+      </c>
+      <c r="E418" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="D419" t="n">
+        <v>26435625</v>
+      </c>
+      <c r="E419" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D420" t="n">
+        <v>17656635</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11726,6 +11726,168 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="D421" t="n">
+        <v>279882322</v>
+      </c>
+      <c r="E421" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D422" t="n">
+        <v>245973201</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="D423" t="n">
+        <v>79212029</v>
+      </c>
+      <c r="E423" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="D424" t="n">
+        <v>36237657</v>
+      </c>
+      <c r="E424" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="D425" t="n">
+        <v>26427225</v>
+      </c>
+      <c r="E425" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D426" t="n">
+        <v>17653835</v>
+      </c>
+      <c r="E426" t="n">
+        <v>0</v>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11888,6 +11888,168 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="D427" t="n">
+        <v>279882322</v>
+      </c>
+      <c r="E427" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D428" t="n">
+        <v>245973201</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="D429" t="n">
+        <v>79212029</v>
+      </c>
+      <c r="E429" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="D430" t="n">
+        <v>36237657</v>
+      </c>
+      <c r="E430" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="D431" t="n">
+        <v>26427225</v>
+      </c>
+      <c r="E431" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D432" t="n">
+        <v>17653835</v>
+      </c>
+      <c r="E432" t="n">
+        <v>0</v>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G432"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12050,6 +12050,184 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="D433" t="n">
+        <v>370182314</v>
+      </c>
+      <c r="E433" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="D434" t="n">
+        <v>167547503</v>
+      </c>
+      <c r="E434" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="D435" t="n">
+        <v>63810284</v>
+      </c>
+      <c r="E435" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D436" t="n">
+        <v>30823239</v>
+      </c>
+      <c r="E436" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="D437" t="n">
+        <v>18353594</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>157.8</v>
+      </c>
+      <c r="D438" t="n">
+        <v>12411214</v>
+      </c>
+      <c r="E438" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12228,6 +12228,168 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="D439" t="n">
+        <v>242887354</v>
+      </c>
+      <c r="E439" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="D440" t="n">
+        <v>158569507</v>
+      </c>
+      <c r="E440" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="D441" t="n">
+        <v>33366101</v>
+      </c>
+      <c r="E441" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>474</v>
+      </c>
+      <c r="D442" t="n">
+        <v>21362880</v>
+      </c>
+      <c r="E442" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="D443" t="n">
+        <v>15912302</v>
+      </c>
+      <c r="E443" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="D444" t="n">
+        <v>9742490</v>
+      </c>
+      <c r="E444" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12390,6 +12390,168 @@
         </is>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="D445" t="n">
+        <v>197219602</v>
+      </c>
+      <c r="E445" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="D446" t="n">
+        <v>147614646</v>
+      </c>
+      <c r="E446" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="D447" t="n">
+        <v>66379971</v>
+      </c>
+      <c r="E447" t="n">
+        <v>-7.05</v>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="D448" t="n">
+        <v>40536626</v>
+      </c>
+      <c r="E448" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="D449" t="n">
+        <v>16178089</v>
+      </c>
+      <c r="E449" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="D450" t="n">
+        <v>14301334</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G450"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12552,6 +12552,172 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="D451" t="n">
+        <v>232993324</v>
+      </c>
+      <c r="E451" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="D452" t="n">
+        <v>87140868</v>
+      </c>
+      <c r="E452" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="D453" t="n">
+        <v>63252932</v>
+      </c>
+      <c r="E453" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="D454" t="n">
+        <v>22888928</v>
+      </c>
+      <c r="E454" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D455" t="n">
+        <v>16630615</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="D456" t="n">
+        <v>16430698</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12718,6 +12718,168 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D457" t="n">
+        <v>193006026</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="D458" t="n">
+        <v>100081028</v>
+      </c>
+      <c r="E458" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D459" t="n">
+        <v>32839785</v>
+      </c>
+      <c r="E459" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="D460" t="n">
+        <v>22960603</v>
+      </c>
+      <c r="E460" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="D461" t="n">
+        <v>13599908</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0</v>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D462" t="n">
+        <v>10607473</v>
+      </c>
+      <c r="E462" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12880,6 +12880,168 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D463" t="n">
+        <v>192790026</v>
+      </c>
+      <c r="E463" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="D464" t="n">
+        <v>100009828</v>
+      </c>
+      <c r="E464" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D465" t="n">
+        <v>32833485</v>
+      </c>
+      <c r="E465" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="D466" t="n">
+        <v>22959603</v>
+      </c>
+      <c r="E466" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="D467" t="n">
+        <v>13598408</v>
+      </c>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D468" t="n">
+        <v>10606273</v>
+      </c>
+      <c r="E468" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G468"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13042,6 +13042,168 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D469" t="n">
+        <v>192790026</v>
+      </c>
+      <c r="E469" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="D470" t="n">
+        <v>100009828</v>
+      </c>
+      <c r="E470" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="D471" t="n">
+        <v>32833485</v>
+      </c>
+      <c r="E471" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="D472" t="n">
+        <v>22959603</v>
+      </c>
+      <c r="E472" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="D473" t="n">
+        <v>13598408</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0</v>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D474" t="n">
+        <v>10606273</v>
+      </c>
+      <c r="E474" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13204,6 +13204,172 @@
         </is>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="D475" t="n">
+        <v>394625581</v>
+      </c>
+      <c r="E475" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="D476" t="n">
+        <v>274947607</v>
+      </c>
+      <c r="E476" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="D477" t="n">
+        <v>65387089</v>
+      </c>
+      <c r="E477" t="n">
+        <v>3</v>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>443</v>
+      </c>
+      <c r="D478" t="n">
+        <v>14455552</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="D479" t="n">
+        <v>12937563</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="D480" t="n">
+        <v>12447861</v>
+      </c>
+      <c r="E480" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G480"/>
+  <dimension ref="A1:G486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13370,6 +13370,168 @@
         </is>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="D481" t="n">
+        <v>521637128</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="D482" t="n">
+        <v>227304562</v>
+      </c>
+      <c r="E482" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="D483" t="n">
+        <v>63694323</v>
+      </c>
+      <c r="E483" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>447.2</v>
+      </c>
+      <c r="D484" t="n">
+        <v>18143997</v>
+      </c>
+      <c r="E484" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="D485" t="n">
+        <v>15924123</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>162</v>
+      </c>
+      <c r="D486" t="n">
+        <v>8011395</v>
+      </c>
+      <c r="E486" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G486"/>
+  <dimension ref="A1:G492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13532,6 +13532,180 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="D487" t="n">
+        <v>482249702</v>
+      </c>
+      <c r="E487" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D488" t="n">
+        <v>394939486</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D489" t="n">
+        <v>81345360</v>
+      </c>
+      <c r="E489" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="D490" t="n">
+        <v>36205493</v>
+      </c>
+      <c r="E490" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D491" t="n">
+        <v>35589277</v>
+      </c>
+      <c r="E491" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="D492" t="n">
+        <v>20529450</v>
+      </c>
+      <c r="E492" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G492"/>
+  <dimension ref="A1:G498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13706,6 +13706,168 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D493" t="n">
+        <v>400904777</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="D494" t="n">
+        <v>242298626</v>
+      </c>
+      <c r="E494" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="D495" t="n">
+        <v>50353985</v>
+      </c>
+      <c r="E495" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>471.8</v>
+      </c>
+      <c r="D496" t="n">
+        <v>31792979</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="D497" t="n">
+        <v>26511489</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="D498" t="n">
+        <v>21290781</v>
+      </c>
+      <c r="E498" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G498"/>
+  <dimension ref="A1:G504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13868,6 +13868,168 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="D499" t="n">
+        <v>414222966</v>
+      </c>
+      <c r="E499" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D500" t="n">
+        <v>289828983</v>
+      </c>
+      <c r="E500" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D501" t="n">
+        <v>50465400</v>
+      </c>
+      <c r="E501" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="D502" t="n">
+        <v>31101240</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="D503" t="n">
+        <v>27657478</v>
+      </c>
+      <c r="E503" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="D504" t="n">
+        <v>21452178</v>
+      </c>
+      <c r="E504" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G504"/>
+  <dimension ref="A1:G510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14030,6 +14030,168 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="D505" t="n">
+        <v>414222166</v>
+      </c>
+      <c r="E505" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D506" t="n">
+        <v>289808983</v>
+      </c>
+      <c r="E506" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D507" t="n">
+        <v>50464900</v>
+      </c>
+      <c r="E507" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="D508" t="n">
+        <v>31100240</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="D509" t="n">
+        <v>27656478</v>
+      </c>
+      <c r="E509" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="D510" t="n">
+        <v>21451778</v>
+      </c>
+      <c r="E510" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G510"/>
+  <dimension ref="A1:G516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14192,6 +14192,168 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="D511" t="n">
+        <v>414222166</v>
+      </c>
+      <c r="E511" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D512" t="n">
+        <v>289808983</v>
+      </c>
+      <c r="E512" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D513" t="n">
+        <v>50464900</v>
+      </c>
+      <c r="E513" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="D514" t="n">
+        <v>31100240</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="D515" t="n">
+        <v>27656478</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="D516" t="n">
+        <v>21451778</v>
+      </c>
+      <c r="E516" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G516"/>
+  <dimension ref="A1:G522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14354,6 +14354,172 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="D517" t="n">
+        <v>291271651</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D518" t="n">
+        <v>197134261</v>
+      </c>
+      <c r="E518" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="D519" t="n">
+        <v>39105288</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="D520" t="n">
+        <v>38650010</v>
+      </c>
+      <c r="E520" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="D521" t="n">
+        <v>17730091</v>
+      </c>
+      <c r="E521" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="D522" t="n">
+        <v>12417942</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G522"/>
+  <dimension ref="A1:G528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14520,6 +14520,168 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D523" t="n">
+        <v>292789577</v>
+      </c>
+      <c r="E523" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="D524" t="n">
+        <v>154556311</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0</v>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="D525" t="n">
+        <v>45158770</v>
+      </c>
+      <c r="E525" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="D526" t="n">
+        <v>27431403</v>
+      </c>
+      <c r="E526" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D527" t="n">
+        <v>24860119</v>
+      </c>
+      <c r="E527" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="D528" t="n">
+        <v>13395026</v>
+      </c>
+      <c r="E528" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G528"/>
+  <dimension ref="A1:G534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14682,6 +14682,168 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D529" t="n">
+        <v>248228281</v>
+      </c>
+      <c r="E529" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="D530" t="n">
+        <v>140378892</v>
+      </c>
+      <c r="E530" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="D531" t="n">
+        <v>39990799</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>492.2</v>
+      </c>
+      <c r="D532" t="n">
+        <v>25662578</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="D533" t="n">
+        <v>23151026</v>
+      </c>
+      <c r="E533" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D534" t="n">
+        <v>15747198</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G534"/>
+  <dimension ref="A1:G540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14844,6 +14844,168 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D535" t="n">
+        <v>208085592</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="D536" t="n">
+        <v>171820604</v>
+      </c>
+      <c r="E536" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="D537" t="n">
+        <v>23763601</v>
+      </c>
+      <c r="E537" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>92</v>
+      </c>
+      <c r="D538" t="n">
+        <v>21474225</v>
+      </c>
+      <c r="E538" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>480.4</v>
+      </c>
+      <c r="D539" t="n">
+        <v>17740398</v>
+      </c>
+      <c r="E539" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="D540" t="n">
+        <v>16870539</v>
+      </c>
+      <c r="E540" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G540"/>
+  <dimension ref="A1:G546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15006,6 +15006,168 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D541" t="n">
+        <v>177249304</v>
+      </c>
+      <c r="E541" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="D542" t="n">
+        <v>148234531</v>
+      </c>
+      <c r="E542" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D543" t="n">
+        <v>28419307</v>
+      </c>
+      <c r="E543" t="n">
+        <v>0</v>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="D544" t="n">
+        <v>16320039</v>
+      </c>
+      <c r="E544" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="D545" t="n">
+        <v>14669577</v>
+      </c>
+      <c r="E545" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="D546" t="n">
+        <v>11751047</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G546"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15168,6 +15168,168 @@
         </is>
       </c>
     </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D547" t="n">
+        <v>177039304</v>
+      </c>
+      <c r="E547" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="D548" t="n">
+        <v>148233931</v>
+      </c>
+      <c r="E548" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D549" t="n">
+        <v>28419007</v>
+      </c>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="D550" t="n">
+        <v>16319939</v>
+      </c>
+      <c r="E550" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="D551" t="n">
+        <v>14668177</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="D552" t="n">
+        <v>11750647</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15330,6 +15330,168 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D553" t="n">
+        <v>177039304</v>
+      </c>
+      <c r="E553" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="D554" t="n">
+        <v>148233931</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D555" t="n">
+        <v>28419007</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0</v>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="D556" t="n">
+        <v>16319939</v>
+      </c>
+      <c r="E556" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="D557" t="n">
+        <v>14668177</v>
+      </c>
+      <c r="E557" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="D558" t="n">
+        <v>11750647</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G558"/>
+  <dimension ref="A1:G564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15492,6 +15492,168 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="D559" t="n">
+        <v>149703382</v>
+      </c>
+      <c r="E559" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="D560" t="n">
+        <v>131565154</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D561" t="n">
+        <v>25201862</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="D562" t="n">
+        <v>15509424</v>
+      </c>
+      <c r="E562" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D563" t="n">
+        <v>11304355</v>
+      </c>
+      <c r="E563" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="D564" t="n">
+        <v>8270403</v>
+      </c>
+      <c r="E564" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G564"/>
+  <dimension ref="A1:G570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15654,6 +15654,168 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="D565" t="n">
+        <v>126200991</v>
+      </c>
+      <c r="E565" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="D566" t="n">
+        <v>120335668</v>
+      </c>
+      <c r="E566" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="D567" t="n">
+        <v>33421904</v>
+      </c>
+      <c r="E567" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>470.8</v>
+      </c>
+      <c r="D568" t="n">
+        <v>19558379</v>
+      </c>
+      <c r="E568" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D569" t="n">
+        <v>9910609</v>
+      </c>
+      <c r="E569" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="D570" t="n">
+        <v>9780226</v>
+      </c>
+      <c r="E570" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G570"/>
+  <dimension ref="A1:G576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15816,6 +15816,168 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D571" t="n">
+        <v>113806045</v>
+      </c>
+      <c r="E571" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D572" t="n">
+        <v>106976643</v>
+      </c>
+      <c r="E572" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="D573" t="n">
+        <v>33457066</v>
+      </c>
+      <c r="E573" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="D574" t="n">
+        <v>27596615</v>
+      </c>
+      <c r="E574" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D575" t="n">
+        <v>10269062</v>
+      </c>
+      <c r="E575" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D576" t="n">
+        <v>7210163</v>
+      </c>
+      <c r="E576" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G576"/>
+  <dimension ref="A1:G582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15978,6 +15978,168 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="D577" t="n">
+        <v>149564111</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="D578" t="n">
+        <v>116429640</v>
+      </c>
+      <c r="E578" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>441</v>
+      </c>
+      <c r="D579" t="n">
+        <v>66424723</v>
+      </c>
+      <c r="E579" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="D580" t="n">
+        <v>21499871</v>
+      </c>
+      <c r="E580" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="D581" t="n">
+        <v>11982274</v>
+      </c>
+      <c r="E581" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>163</v>
+      </c>
+      <c r="D582" t="n">
+        <v>7978564</v>
+      </c>
+      <c r="E582" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G582"/>
+  <dimension ref="A1:G588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16140,6 +16140,168 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="D583" t="n">
+        <v>137133813</v>
+      </c>
+      <c r="E583" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="D584" t="n">
+        <v>91057676</v>
+      </c>
+      <c r="E584" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="D585" t="n">
+        <v>75329530</v>
+      </c>
+      <c r="E585" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>440</v>
+      </c>
+      <c r="D586" t="n">
+        <v>30601160</v>
+      </c>
+      <c r="E586" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="D587" t="n">
+        <v>11917806</v>
+      </c>
+      <c r="E587" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="D588" t="n">
+        <v>6738838</v>
+      </c>
+      <c r="E588" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G588"/>
+  <dimension ref="A1:G594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16302,6 +16302,168 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="D589" t="n">
+        <v>137015813</v>
+      </c>
+      <c r="E589" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="D590" t="n">
+        <v>91055676</v>
+      </c>
+      <c r="E590" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="D591" t="n">
+        <v>75329330</v>
+      </c>
+      <c r="E591" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>440</v>
+      </c>
+      <c r="D592" t="n">
+        <v>30601060</v>
+      </c>
+      <c r="E592" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="D593" t="n">
+        <v>11917106</v>
+      </c>
+      <c r="E593" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="D594" t="n">
+        <v>6724838</v>
+      </c>
+      <c r="E594" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G594"/>
+  <dimension ref="A1:G600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16464,6 +16464,168 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="D595" t="n">
+        <v>137015813</v>
+      </c>
+      <c r="E595" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="D596" t="n">
+        <v>91055676</v>
+      </c>
+      <c r="E596" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="D597" t="n">
+        <v>75329330</v>
+      </c>
+      <c r="E597" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>440</v>
+      </c>
+      <c r="D598" t="n">
+        <v>30601060</v>
+      </c>
+      <c r="E598" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="D599" t="n">
+        <v>11917106</v>
+      </c>
+      <c r="E599" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="D600" t="n">
+        <v>6724838</v>
+      </c>
+      <c r="E600" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G600"/>
+  <dimension ref="A1:G606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16626,6 +16626,168 @@
         </is>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D601" t="n">
+        <v>164144134</v>
+      </c>
+      <c r="E601" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="D602" t="n">
+        <v>100097535</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="D603" t="n">
+        <v>26917511</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>446.4</v>
+      </c>
+      <c r="D604" t="n">
+        <v>19839108</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>90.05</v>
+      </c>
+      <c r="D605" t="n">
+        <v>12868474</v>
+      </c>
+      <c r="E605" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="D606" t="n">
+        <v>7607874</v>
+      </c>
+      <c r="E606" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G606"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16788,6 +16788,168 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="D607" t="n">
+        <v>179217411</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="D608" t="n">
+        <v>171072452</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>85.55</v>
+      </c>
+      <c r="D609" t="n">
+        <v>52934212</v>
+      </c>
+      <c r="E609" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>442.4</v>
+      </c>
+      <c r="D610" t="n">
+        <v>23220078</v>
+      </c>
+      <c r="E610" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>90</v>
+      </c>
+      <c r="D611" t="n">
+        <v>12299489</v>
+      </c>
+      <c r="E611" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="D612" t="n">
+        <v>5726985</v>
+      </c>
+      <c r="E612" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16950,6 +16950,172 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="D613" t="n">
+        <v>339876011</v>
+      </c>
+      <c r="E613" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="D614" t="n">
+        <v>187891158</v>
+      </c>
+      <c r="E614" t="n">
+        <v>1</v>
+      </c>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="D615" t="n">
+        <v>36758866</v>
+      </c>
+      <c r="E615" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>447.2</v>
+      </c>
+      <c r="D616" t="n">
+        <v>19774087</v>
+      </c>
+      <c r="E616" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="D617" t="n">
+        <v>9395361</v>
+      </c>
+      <c r="E617" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="D618" t="n">
+        <v>8433659</v>
+      </c>
+      <c r="E618" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G618"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17116,6 +17116,168 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D619" t="n">
+        <v>237945061</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="D620" t="n">
+        <v>178685584</v>
+      </c>
+      <c r="E620" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="D621" t="n">
+        <v>28598952</v>
+      </c>
+      <c r="E621" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>451.4</v>
+      </c>
+      <c r="D622" t="n">
+        <v>19622598</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D623" t="n">
+        <v>14725223</v>
+      </c>
+      <c r="E623" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="D624" t="n">
+        <v>9509222</v>
+      </c>
+      <c r="E624" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G624"/>
+  <dimension ref="A1:G630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17278,6 +17278,172 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D625" t="n">
+        <v>238011878</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="D626" t="n">
+        <v>180386553</v>
+      </c>
+      <c r="E626" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>85</v>
+      </c>
+      <c r="D627" t="n">
+        <v>42941090</v>
+      </c>
+      <c r="E627" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>457</v>
+      </c>
+      <c r="D628" t="n">
+        <v>22327006</v>
+      </c>
+      <c r="E628" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="D629" t="n">
+        <v>14351523</v>
+      </c>
+      <c r="E629" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D630" t="n">
+        <v>11361151</v>
+      </c>
+      <c r="E630" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G630"/>
+  <dimension ref="A1:G636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17444,6 +17444,172 @@
         </is>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D631" t="n">
+        <v>238009878</v>
+      </c>
+      <c r="E631" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="D632" t="n">
+        <v>180377953</v>
+      </c>
+      <c r="E632" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>85</v>
+      </c>
+      <c r="D633" t="n">
+        <v>42935990</v>
+      </c>
+      <c r="E633" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>457</v>
+      </c>
+      <c r="D634" t="n">
+        <v>22326906</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="D635" t="n">
+        <v>14344823</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D636" t="n">
+        <v>11360351</v>
+      </c>
+      <c r="E636" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G636"/>
+  <dimension ref="A1:G642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17610,6 +17610,172 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D637" t="n">
+        <v>238009878</v>
+      </c>
+      <c r="E637" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="D638" t="n">
+        <v>180377953</v>
+      </c>
+      <c r="E638" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>85</v>
+      </c>
+      <c r="D639" t="n">
+        <v>42935990</v>
+      </c>
+      <c r="E639" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>457</v>
+      </c>
+      <c r="D640" t="n">
+        <v>22326906</v>
+      </c>
+      <c r="E640" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="D641" t="n">
+        <v>14344823</v>
+      </c>
+      <c r="E641" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D642" t="n">
+        <v>11360351</v>
+      </c>
+      <c r="E642" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G642"/>
+  <dimension ref="A1:G648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17776,6 +17776,168 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="D643" t="n">
+        <v>239550549</v>
+      </c>
+      <c r="E643" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D644" t="n">
+        <v>158055822</v>
+      </c>
+      <c r="E644" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D645" t="n">
+        <v>45981032</v>
+      </c>
+      <c r="E645" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>440</v>
+      </c>
+      <c r="D646" t="n">
+        <v>29180102</v>
+      </c>
+      <c r="E646" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="D647" t="n">
+        <v>18188585</v>
+      </c>
+      <c r="E647" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D648" t="n">
+        <v>10631099</v>
+      </c>
+      <c r="E648" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G648"/>
+  <dimension ref="A1:G654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17938,6 +17938,168 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="D649" t="n">
+        <v>192122330</v>
+      </c>
+      <c r="E649" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="D650" t="n">
+        <v>91023973</v>
+      </c>
+      <c r="E650" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="D651" t="n">
+        <v>81490138</v>
+      </c>
+      <c r="E651" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D652" t="n">
+        <v>19581215</v>
+      </c>
+      <c r="E652" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>442</v>
+      </c>
+      <c r="D653" t="n">
+        <v>13032108</v>
+      </c>
+      <c r="E653" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="D654" t="n">
+        <v>7586311</v>
+      </c>
+      <c r="E654" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G654"/>
+  <dimension ref="A1:G660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18100,6 +18100,168 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="D655" t="n">
+        <v>142478217</v>
+      </c>
+      <c r="E655" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="D656" t="n">
+        <v>138555273</v>
+      </c>
+      <c r="E656" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="D657" t="n">
+        <v>30349391</v>
+      </c>
+      <c r="E657" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D658" t="n">
+        <v>18686686</v>
+      </c>
+      <c r="E658" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>445.4</v>
+      </c>
+      <c r="D659" t="n">
+        <v>14634642</v>
+      </c>
+      <c r="E659" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="D660" t="n">
+        <v>8208758</v>
+      </c>
+      <c r="E660" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G660"/>
+  <dimension ref="A1:G666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18262,6 +18262,144 @@
         </is>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
+      <c r="D661" t="n">
+        <v>198830189</v>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="n">
+        <v>145687128</v>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="n">
+        <v>27631300</v>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
+      <c r="D664" t="n">
+        <v>18104204</v>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr"/>
+      <c r="D665" t="n">
+        <v>11487200</v>
+      </c>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr"/>
+      <c r="D666" t="n">
+        <v>4568298</v>
+      </c>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G666"/>
+  <dimension ref="A1:G672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18400,6 +18400,144 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="n">
+        <v>212829907</v>
+      </c>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="n">
+        <v>85332131</v>
+      </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="n">
+        <v>33410603</v>
+      </c>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="n">
+        <v>27742575</v>
+      </c>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="n">
+        <v>10946548</v>
+      </c>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="n">
+        <v>7129035</v>
+      </c>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G672"/>
+  <dimension ref="A1:G678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18538,6 +18538,168 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D673" t="n">
+        <v>212816907</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D674" t="n">
+        <v>85331331</v>
+      </c>
+      <c r="E674" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D675" t="n">
+        <v>33410203</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0</v>
+      </c>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="D676" t="n">
+        <v>27742475</v>
+      </c>
+      <c r="E676" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="D677" t="n">
+        <v>10946448</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D678" t="n">
+        <v>7128635</v>
+      </c>
+      <c r="E678" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G678"/>
+  <dimension ref="A1:G684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18700,6 +18700,168 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D679" t="n">
+        <v>212816907</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="D680" t="n">
+        <v>85331331</v>
+      </c>
+      <c r="E680" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>33410203</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0</v>
+      </c>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>455.2</v>
+      </c>
+      <c r="D682" t="n">
+        <v>27742475</v>
+      </c>
+      <c r="E682" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="D683" t="n">
+        <v>10946448</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D684" t="n">
+        <v>7128635</v>
+      </c>
+      <c r="E684" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G684"/>
+  <dimension ref="A1:G690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18862,6 +18862,144 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="n">
+        <v>526179475</v>
+      </c>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="n">
+        <v>91960116</v>
+      </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="n">
+        <v>90331600</v>
+      </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="n">
+        <v>43268405</v>
+      </c>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="n">
+        <v>20154770</v>
+      </c>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="n">
+        <v>6469275</v>
+      </c>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G690"/>
+  <dimension ref="A1:G696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19000,6 +19000,168 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D691" t="n">
+        <v>308091718</v>
+      </c>
+      <c r="E691" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="D692" t="n">
+        <v>86643519</v>
+      </c>
+      <c r="E692" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="D693" t="n">
+        <v>52934330</v>
+      </c>
+      <c r="E693" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="D694" t="n">
+        <v>31703920</v>
+      </c>
+      <c r="E694" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="D695" t="n">
+        <v>20290981</v>
+      </c>
+      <c r="E695" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="D696" t="n">
+        <v>11448136</v>
+      </c>
+      <c r="E696" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G696"/>
+  <dimension ref="A1:G702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19162,6 +19162,168 @@
         </is>
       </c>
     </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="D697" t="n">
+        <v>184557050</v>
+      </c>
+      <c r="E697" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="D698" t="n">
+        <v>115696798</v>
+      </c>
+      <c r="E698" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="D699" t="n">
+        <v>51240808</v>
+      </c>
+      <c r="E699" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="D700" t="n">
+        <v>26685730</v>
+      </c>
+      <c r="E700" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="D701" t="n">
+        <v>21341428</v>
+      </c>
+      <c r="E701" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="D702" t="n">
+        <v>9494989</v>
+      </c>
+      <c r="E702" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G702"/>
+  <dimension ref="A1:G708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19324,6 +19324,168 @@
         </is>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="D703" t="n">
+        <v>245668410</v>
+      </c>
+      <c r="E703" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="D704" t="n">
+        <v>117456362</v>
+      </c>
+      <c r="E704" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="D705" t="n">
+        <v>31031252</v>
+      </c>
+      <c r="E705" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>433</v>
+      </c>
+      <c r="D706" t="n">
+        <v>17387196</v>
+      </c>
+      <c r="E706" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D707" t="n">
+        <v>17224479</v>
+      </c>
+      <c r="E707" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="D708" t="n">
+        <v>13990543</v>
+      </c>
+      <c r="E708" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G708"/>
+  <dimension ref="A1:G714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19486,6 +19486,176 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="D709" t="n">
+        <v>320572344</v>
+      </c>
+      <c r="E709" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="D710" t="n">
+        <v>178924091</v>
+      </c>
+      <c r="E710" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="D711" t="n">
+        <v>55906540</v>
+      </c>
+      <c r="E711" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="D712" t="n">
+        <v>30854916</v>
+      </c>
+      <c r="E712" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="D713" t="n">
+        <v>24026386</v>
+      </c>
+      <c r="E713" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D714" t="n">
+        <v>21025766</v>
+      </c>
+      <c r="E714" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G714"/>
+  <dimension ref="A1:G720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19656,6 +19656,176 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="D715" t="n">
+        <v>320533344</v>
+      </c>
+      <c r="E715" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="D716" t="n">
+        <v>178857691</v>
+      </c>
+      <c r="E716" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="D717" t="n">
+        <v>55906440</v>
+      </c>
+      <c r="E717" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="D718" t="n">
+        <v>30851316</v>
+      </c>
+      <c r="E718" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="D719" t="n">
+        <v>24025286</v>
+      </c>
+      <c r="E719" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D720" t="n">
+        <v>20988366</v>
+      </c>
+      <c r="E720" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G720"/>
+  <dimension ref="A1:G726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19826,6 +19826,176 @@
         </is>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="D721" t="n">
+        <v>320533344</v>
+      </c>
+      <c r="E721" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="D722" t="n">
+        <v>178857691</v>
+      </c>
+      <c r="E722" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="D723" t="n">
+        <v>55906440</v>
+      </c>
+      <c r="E723" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="D724" t="n">
+        <v>30851316</v>
+      </c>
+      <c r="E724" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="D725" t="n">
+        <v>24025286</v>
+      </c>
+      <c r="E725" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="D726" t="n">
+        <v>20988366</v>
+      </c>
+      <c r="E726" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
